--- a/Week_02 - Hello, Machine Learning/Engineering/ml_lib_model_report.xlsx
+++ b/Week_02 - Hello, Machine Learning/Engineering/ml_lib_model_report.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>k</t>
   </si>
@@ -28,6 +28,12 @@
   </si>
   <si>
     <t>test_accuracy</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>With my implementation of KNN the best model is, strangely, the one with k=7. It acheives the same accuracy on the test set, as the scikit-learn KNN with k=5. I am unsure why with k=2 it has train accuracy =1.  It took it a lot longer to train, so it needs some optimization</t>
   </si>
 </sst>
 </file>
@@ -57,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -65,13 +71,175 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -384,14 +552,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="16.7109375" customWidth="1"/>
     <col min="3" max="3" width="13.140625" customWidth="1"/>
+    <col min="21" max="21" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -401,8 +570,13 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T1" s="4"/>
+      <c r="U1" s="5"/>
+    </row>
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -412,8 +586,13 @@
       <c r="C2">
         <v>0.86086086086086089</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S2" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="T2" s="2"/>
+      <c r="U2" s="7"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -423,8 +602,11 @@
       <c r="C3">
         <v>0.86086086086086089</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S3" s="6"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="7"/>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -434,8 +616,11 @@
       <c r="C4">
         <v>0.89389389389389384</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S4" s="6"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="7"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -445,8 +630,11 @@
       <c r="C5">
         <v>0.89089089089089091</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S5" s="6"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="7"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -456,8 +644,11 @@
       <c r="C6">
         <v>0.89489489489489493</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S6" s="6"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="7"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -467,8 +658,11 @@
       <c r="C7">
         <v>0.89489489489489493</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S7" s="6"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="7"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -478,8 +672,11 @@
       <c r="C8" s="1">
         <v>0.89589589589589591</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S8" s="6"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="7"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -489,8 +686,11 @@
       <c r="C9">
         <v>0.89489489489489493</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S9" s="6"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="7"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -500,8 +700,11 @@
       <c r="C10">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S10" s="6"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="7"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -511,8 +714,11 @@
       <c r="C11">
         <v>0.89189189189189189</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S11" s="6"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="7"/>
+    </row>
+    <row r="12" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -522,8 +728,11 @@
       <c r="C12">
         <v>0.88888888888888884</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="S12" s="8"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="10"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -534,7 +743,7 @@
         <v>0.88688688688688688</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -545,7 +754,7 @@
         <v>0.88988988988988993</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -556,7 +765,7 @@
         <v>0.88688688688688688</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -667,6 +876,10 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="S2:U12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing r:id="rId1"/>
 </worksheet>
